--- a/astro-site/public/dl/kit-tareas-restaurante-creativo/02-mise-en-place-degustacion.xlsx
+++ b/astro-site/public/dl/kit-tareas-restaurante-creativo/02-mise-en-place-degustacion.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pre-elab Largo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pre-elab Medio" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Pre-elab Día" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Plating Bible" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-elab Largo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-elab Medio" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-elab Día" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plating Bible" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Pre-elab Largo'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Pre-elab Medio'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Pre-elab Día'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Plating Bible'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,6 +87,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -152,57 +162,68 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -562,15 +583,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -578,6 +600,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -613,9 +636,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -651,8 +672,25 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-restaurante-creativo · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -661,18 +699,18 @@
   <sheetPr>
     <tabColor rgb="003F51B5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -689,6 +727,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -828,6 +867,7 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -986,6 +1026,7 @@
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="13" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
@@ -1124,6 +1165,26 @@
       <c r="E27" s="12" t="n"/>
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C28">
+        <f>COUNTIF(E6:E27,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E28">
+        <f>COUNTIF(B6:B27,"?*")</f>
+        <v>18.0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -1149,12 +1210,26 @@
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G27">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E19 E23 E24 E25 E26 E27" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E19 E23 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1163,18 +1238,18 @@
   <sheetPr>
     <tabColor rgb="003F51B5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1191,6 +1266,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1349,6 +1425,7 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -1468,6 +1545,26 @@
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="13" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C19">
+        <f>COUNTIF(E6:E18,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E19">
+        <f>COUNTIF(B6:B18,"?*")</f>
+        <v>11.0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -1492,12 +1589,26 @@
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A13:G13"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1506,18 +1617,18 @@
   <sheetPr>
     <tabColor rgb="003F51B5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1534,6 +1645,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1673,6 +1785,7 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -1812,6 +1925,7 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="13" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -1969,6 +2083,26 @@
       <c r="E27" s="12" t="n"/>
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C28">
+        <f>COUNTIF(E6:E27,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E28">
+        <f>COUNTIF(B6:B27,"?*")</f>
+        <v>18.0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -1994,12 +2128,26 @@
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G27">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25 E26 E27" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2008,18 +2156,18 @@
   <sheetPr>
     <tabColor rgb="003F51B5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2036,6 +2184,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -2327,6 +2476,7 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="13" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -2503,6 +2653,26 @@
       <c r="E28" s="12" t="n"/>
       <c r="F28" s="11" t="n"/>
       <c r="G28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C29">
+        <f>COUNTIF(E6:E28,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E29">
+        <f>COUNTIF(B6:B28,"?*")</f>
+        <v>21.0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -2527,11 +2697,25 @@
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G28">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E22 E23 E24 E25 E26 E27 E28" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E22 E23 E24 E25 E26 E27 E28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-restaurante-creativo/02-mise-en-place-degustacion.xlsx
+++ b/astro-site/public/dl/kit-tareas-restaurante-creativo/02-mise-en-place-degustacion.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -674,9 +674,38 @@
     </row>
     <row r="15"/>
     <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-restaurante-creativo · info@aichef.pro</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Pescado crudo y producto que va crudo al plato:</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>▸ Todo pescado que se sirva crudo o semicrudo (tartar, ceviche, marinado, curado, ahumado en frío) necesita congelación previa: ≥24 h a −20 °C o 15 h a −35 °C. Pide el certificado al proveedor y anota el lote; el cítrico del ceviche NO mata el anisakis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>▸ Microbrotes, flores comestibles y hierbas van crudos al pase y no reciben ningún tratamiento térmico después: se desinfectan y se ACLARAN con agua potable antes de entrar en la estación de emplatado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-restaurante-creativo · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -975,7 +1004,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Marinados largos (carnes/pescados en aceite, sal, especias)</t>
+          <t>Marinados largos (carnes/pescados en aceite, sal, especias): el pescado que no se cocine por encima de 60 °C —marinado, curado o ahumado en frío— tiene que venir de congelación preventiva frente al ANISAKIS (ver «Pre-elab Día»)</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1173,8 +1202,8 @@
         </is>
       </c>
       <c r="C28">
-        <f>COUNTIF(E6:E27,"✓")</f>
-        <v>2.0</v>
+        <f>COUNTIFS(B6:B27,"?*",E6:E27,"✓")-COUNTIFS(B6:B27,"Tarea",E6:E27,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1182,8 +1211,8 @@
         </is>
       </c>
       <c r="E28">
-        <f>COUNTIF(B6:B27,"?*")</f>
-        <v>18.0</v>
+        <f>COUNTIF(B6:B27,"?*")-COUNTIF(B6:B27,"Tarea")-COUNTIF(E6:E27,"N/A")</f>
+        <v>16.0</v>
       </c>
     </row>
     <row r="29">
@@ -1216,8 +1245,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E19 E23 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E19 E23 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1317,7 +1346,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Huevo sous-vide (63°C / 75 min o según receta)</t>
+          <t>Huevo sous-vide (63 °C / 75 min o según receta)</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1553,8 +1582,8 @@
         </is>
       </c>
       <c r="C19">
-        <f>COUNTIF(E6:E18,"✓")</f>
-        <v>1.0</v>
+        <f>COUNTIFS(B6:B18,"?*",E6:E18,"✓")-COUNTIFS(B6:B18,"Tarea",E6:E18,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1562,8 +1591,8 @@
         </is>
       </c>
       <c r="E19">
-        <f>COUNTIF(B6:B18,"?*")</f>
-        <v>11.0</v>
+        <f>COUNTIF(B6:B18,"?*")-COUNTIF(B6:B18,"Tarea")-COUNTIF(E6:E18,"N/A")</f>
+        <v>10.0</v>
       </c>
     </row>
     <row r="20">
@@ -1595,8 +1624,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1619,7 +1648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1912,7 +1941,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Tartares y ceviches (cortar en el momento, no antes de 2h)</t>
+          <t>Tartares y ceviches: cortar en el momento, nunca más de 2 h antes del pase. Prevención de ANISAKIS: el pescado que se sirve crudo o semicrudo debe haberse congelado antes ≥24 h a −20 °C (o 15 h a −35 °C) — exige el certificado al proveedor o congélalo tú, y anota el lote</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -2014,12 +2043,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Preparar nieves / granizados al momento</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>Pastelería</t>
+          <t>Desinfectar microbrotes, flores comestibles y hierbas que van CRUDOS al plato: lejía apta para uso alimentario según la dosis del fabricante (habitual: 70 ppm, 5 min) y ACLARAR con agua potable abundante</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D24" s="11" t="n"/>
@@ -2033,12 +2062,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Preparar crujientes de última hora (tempura, chip)</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>Cocina</t>
+          <t>Preparar nieves / granizados al momento</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Pastelería</t>
         </is>
       </c>
       <c r="D25" s="11" t="n"/>
@@ -2052,12 +2081,12 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Montar biberones con salsas para emplatado</t>
+          <t>Preparar crujientes de última hora (tempura, chip)</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Emplatado</t>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D26" s="11" t="n"/>
@@ -2071,7 +2100,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Verificar stencils, pinzas, cucharas de autor limpias</t>
+          <t>Montar biberones con salsas para emplatado</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2085,57 +2114,76 @@
       <c r="G27" s="13" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="19" t="inlineStr">
+      <c r="A28" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Verificar stencils, pinzas, cucharas de autor limpias</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Emplatado</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C28">
-        <f>COUNTIF(E6:E27,"✓")</f>
-        <v>2.0</v>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29">
+        <f>COUNTIFS(B6:B28,"?*",E6:E28,"✓")-COUNTIFS(B6:B28,"Tarea",E6:E28,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E28">
-        <f>COUNTIF(B6:B27,"?*")</f>
-        <v>18.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E29">
+        <f>COUNTIF(B6:B28,"?*")-COUNTIF(B6:B28,"Tarea")-COUNTIF(E6:E28,"N/A")</f>
+        <v>17.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A29:G29"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G27">
+  <conditionalFormatting sqref="A6:G28">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25 E26 E27 E28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2661,8 +2709,8 @@
         </is>
       </c>
       <c r="C29">
-        <f>COUNTIF(E6:E28,"✓")</f>
-        <v>1.0</v>
+        <f>COUNTIFS(B6:B28,"?*",E6:E28,"✓")-COUNTIFS(B6:B28,"Tarea",E6:E28,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2670,8 +2718,8 @@
         </is>
       </c>
       <c r="E29">
-        <f>COUNTIF(B6:B28,"?*")</f>
-        <v>21.0</v>
+        <f>COUNTIF(B6:B28,"?*")-COUNTIF(B6:B28,"Tarea")-COUNTIF(E6:E28,"N/A")</f>
+        <v>20.0</v>
       </c>
     </row>
     <row r="30">
@@ -2703,8 +2751,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E22 E23 E24 E25 E26 E27 E28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E22 E23 E24 E25 E26 E27 E28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-restaurante-creativo/02-mise-en-place-degustacion.xlsx
+++ b/astro-site/public/dl/kit-tareas-restaurante-creativo/02-mise-en-place-degustacion.xlsx
@@ -2170,8 +2170,8 @@
   <mergeCells count="7">
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
